--- a/Scout/crk-vs-marshalltown-092526.xlsx
+++ b/Scout/crk-vs-marshalltown-092526.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R24f1031cb73e4a97"/>
+    <sheet name="Sheet1" sheetId="1" r:id="Reb62fd72e56e4d9e"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -79,9 +94,6 @@
     <t>MOTION DIR</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
     <t>SERIES</t>
   </si>
   <si>
@@ -118,6 +130,9 @@
     <t>Y</t>
   </si>
   <si>
+    <t>G DOT</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
@@ -142,6 +157,9 @@
     <t>ISO @ 4</t>
   </si>
   <si>
+    <t>K DOT</t>
+  </si>
+  <si>
     <t>RUMBLE</t>
   </si>
   <si>
@@ -157,6 +175,9 @@
     <t>D</t>
   </si>
   <si>
+    <t>DOT UNDER</t>
+  </si>
+  <si>
     <t>BAL</t>
   </si>
   <si>
@@ -178,18 +199,27 @@
     <t>ISO @ 3</t>
   </si>
   <si>
+    <t>GUN STACK G</t>
+  </si>
+  <si>
     <t>POWER READ</t>
   </si>
   <si>
     <t>TRAP</t>
   </si>
   <si>
+    <t>GUN STACK K</t>
+  </si>
+  <si>
     <t>QB SWEEP</t>
   </si>
   <si>
     <t>Complete, TD</t>
   </si>
   <si>
+    <t>DOT</t>
+  </si>
+  <si>
     <t>ACE</t>
   </si>
   <si>
@@ -247,6 +277,9 @@
     <t>VERTICAL</t>
   </si>
   <si>
+    <t>G I DOT UNDER</t>
+  </si>
+  <si>
     <t>SPLIT</t>
   </si>
   <si>
@@ -269,6 +302,9 @@
   </si>
   <si>
     <t>GIVE @ 2</t>
+  </si>
+  <si>
+    <t>G DOT UNDER</t>
   </si>
   <si>
     <t>FB TRAP</t>
@@ -293,7 +329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y126"/>
+  <dimension ref="A1:AC126"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -371,6 +407,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -380,7 +428,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -391,7 +439,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -402,7 +450,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5">
@@ -413,19 +461,19 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>-40</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6">
@@ -436,7 +484,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -448,33 +496,36 @@
         <v>-15</v>
       </c>
       <c r="G6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J6">
         <v>17</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
-      </c>
-      <c r="R6" t="s">
-        <v>35</v>
-      </c>
-      <c r="S6" t="s">
-        <v>36</v>
-      </c>
-      <c r="T6" t="s">
-        <v>37</v>
-      </c>
-      <c r="U6" t="s">
-        <v>35</v>
-      </c>
-      <c r="X6">
+        <v>38</v>
+      </c>
+      <c r="P6" t="s">
+        <v>39</v>
+      </c>
+      <c r="W6" t="s">
+        <v>40</v>
+      </c>
+      <c r="X6" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
     </row>
@@ -486,7 +537,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -498,33 +549,36 @@
         <v>-32</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7">
+        <v>3</v>
+      </c>
+      <c r="K7" t="s">
+        <v>45</v>
+      </c>
+      <c r="P7" t="s">
         <v>39</v>
       </c>
-      <c r="J7">
-        <v>3</v>
-      </c>
-      <c r="K7" t="s">
-        <v>40</v>
-      </c>
-      <c r="R7" t="s">
-        <v>31</v>
-      </c>
-      <c r="S7" t="s">
-        <v>41</v>
-      </c>
-      <c r="T7" t="s">
-        <v>42</v>
-      </c>
-      <c r="U7" t="s">
-        <v>35</v>
-      </c>
-      <c r="X7">
+      <c r="W7" t="s">
+        <v>35</v>
+      </c>
+      <c r="X7" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB7">
         <v>1</v>
       </c>
     </row>
@@ -536,7 +590,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -548,33 +602,36 @@
         <v>-35</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>40</v>
-      </c>
-      <c r="R8" t="s">
-        <v>31</v>
-      </c>
-      <c r="S8" t="s">
-        <v>41</v>
-      </c>
-      <c r="T8" t="s">
-        <v>43</v>
-      </c>
-      <c r="U8" t="s">
-        <v>31</v>
-      </c>
-      <c r="X8">
+        <v>45</v>
+      </c>
+      <c r="P8" t="s">
+        <v>48</v>
+      </c>
+      <c r="W8" t="s">
+        <v>35</v>
+      </c>
+      <c r="X8" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
     </row>
@@ -586,7 +643,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -598,33 +655,36 @@
         <v>-35</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I9" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>40</v>
-      </c>
-      <c r="R9" t="s">
-        <v>35</v>
-      </c>
-      <c r="S9" t="s">
-        <v>36</v>
-      </c>
-      <c r="T9" t="s">
-        <v>37</v>
-      </c>
-      <c r="U9" t="s">
-        <v>35</v>
-      </c>
-      <c r="X9">
+        <v>45</v>
+      </c>
+      <c r="P9" t="s">
+        <v>39</v>
+      </c>
+      <c r="W9" t="s">
+        <v>40</v>
+      </c>
+      <c r="X9" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB9">
         <v>1</v>
       </c>
     </row>
@@ -636,7 +696,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -648,15 +708,15 @@
         <v>-35</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="I10" t="s">
-        <v>46</v>
-      </c>
-      <c r="X10">
+        <v>52</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
     </row>
@@ -668,7 +728,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -680,33 +740,36 @@
         <v>-42</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I11" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J11">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>34</v>
-      </c>
-      <c r="R11" t="s">
-        <v>48</v>
-      </c>
-      <c r="S11" t="s">
-        <v>49</v>
-      </c>
-      <c r="U11" t="s">
-        <v>35</v>
-      </c>
-      <c r="V11" t="s">
-        <v>35</v>
-      </c>
-      <c r="X11">
+        <v>38</v>
+      </c>
+      <c r="P11" t="s">
+        <v>54</v>
+      </c>
+      <c r="W11" t="s">
+        <v>55</v>
+      </c>
+      <c r="X11" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB11">
         <v>1</v>
       </c>
     </row>
@@ -718,7 +781,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -730,33 +793,36 @@
         <v>-43</v>
       </c>
       <c r="G12" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I12" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12" t="s">
-        <v>34</v>
-      </c>
-      <c r="R12" t="s">
-        <v>48</v>
-      </c>
-      <c r="S12" t="s">
-        <v>49</v>
-      </c>
-      <c r="U12" t="s">
-        <v>35</v>
-      </c>
-      <c r="V12" t="s">
-        <v>35</v>
-      </c>
-      <c r="X12">
+        <v>38</v>
+      </c>
+      <c r="P12" t="s">
+        <v>54</v>
+      </c>
+      <c r="W12" t="s">
+        <v>55</v>
+      </c>
+      <c r="X12" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB12">
         <v>1</v>
       </c>
     </row>
@@ -768,7 +834,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -780,30 +846,33 @@
         <v>-42</v>
       </c>
       <c r="G13" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J13">
         <v>9</v>
       </c>
       <c r="K13" t="s">
-        <v>34</v>
-      </c>
-      <c r="R13" t="s">
-        <v>35</v>
-      </c>
-      <c r="S13" t="s">
-        <v>50</v>
-      </c>
-      <c r="U13" t="s">
-        <v>35</v>
-      </c>
-      <c r="X13">
+        <v>38</v>
+      </c>
+      <c r="P13" t="s">
+        <v>54</v>
+      </c>
+      <c r="W13" t="s">
+        <v>40</v>
+      </c>
+      <c r="X13" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -815,7 +884,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D14">
         <v>4</v>
@@ -827,30 +896,33 @@
         <v>49</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H14" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I14" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J14">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>40</v>
-      </c>
-      <c r="R14" t="s">
-        <v>48</v>
-      </c>
-      <c r="S14" t="s">
-        <v>49</v>
-      </c>
-      <c r="U14" t="s">
-        <v>35</v>
-      </c>
-      <c r="X14">
+        <v>45</v>
+      </c>
+      <c r="P14" t="s">
+        <v>54</v>
+      </c>
+      <c r="W14" t="s">
+        <v>55</v>
+      </c>
+      <c r="X14" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB14">
         <v>1</v>
       </c>
     </row>
@@ -862,7 +934,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -874,33 +946,36 @@
         <v>48</v>
       </c>
       <c r="G15" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I15" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>34</v>
-      </c>
-      <c r="R15" t="s">
-        <v>48</v>
-      </c>
-      <c r="S15" t="s">
-        <v>49</v>
-      </c>
-      <c r="U15" t="s">
-        <v>35</v>
-      </c>
-      <c r="V15" t="s">
-        <v>35</v>
-      </c>
-      <c r="X15">
+        <v>38</v>
+      </c>
+      <c r="P15" t="s">
+        <v>54</v>
+      </c>
+      <c r="W15" t="s">
+        <v>55</v>
+      </c>
+      <c r="X15" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB15">
         <v>1</v>
       </c>
     </row>
@@ -912,7 +987,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -924,27 +999,30 @@
         <v>48</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H16" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I16" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16" t="s">
-        <v>34</v>
-      </c>
-      <c r="R16" t="s">
-        <v>31</v>
-      </c>
-      <c r="U16" t="s">
-        <v>31</v>
-      </c>
-      <c r="X16">
+        <v>38</v>
+      </c>
+      <c r="P16" t="s">
+        <v>54</v>
+      </c>
+      <c r="W16" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB16">
         <v>1</v>
       </c>
     </row>
@@ -956,7 +1034,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -968,30 +1046,33 @@
         <v>49</v>
       </c>
       <c r="G17" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I17" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J17">
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>34</v>
-      </c>
-      <c r="R17" t="s">
-        <v>35</v>
-      </c>
-      <c r="S17" t="s">
-        <v>50</v>
-      </c>
-      <c r="U17" t="s">
-        <v>31</v>
-      </c>
-      <c r="X17">
+        <v>38</v>
+      </c>
+      <c r="P17" t="s">
+        <v>54</v>
+      </c>
+      <c r="W17" t="s">
+        <v>40</v>
+      </c>
+      <c r="X17" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB17">
         <v>1</v>
       </c>
     </row>
@@ -1003,7 +1084,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D18">
         <v>4</v>
@@ -1015,18 +1096,18 @@
         <v>49</v>
       </c>
       <c r="G18" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H18" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I18" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J18">
         <v>5</v>
       </c>
-      <c r="X18">
+      <c r="AB18">
         <v>1</v>
       </c>
     </row>
@@ -1038,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D19">
         <v>4</v>
@@ -1050,18 +1131,18 @@
         <v>44</v>
       </c>
       <c r="G19" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H19" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I19" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
-      <c r="X19">
+      <c r="AB19">
         <v>1</v>
       </c>
     </row>
@@ -1073,7 +1154,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -1085,15 +1166,15 @@
         <v>44</v>
       </c>
       <c r="G20" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H20" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I20" t="s">
-        <v>29</v>
-      </c>
-      <c r="X20">
+        <v>33</v>
+      </c>
+      <c r="AB20">
         <v>2</v>
       </c>
     </row>
@@ -1105,7 +1186,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1117,33 +1198,36 @@
         <v>-32</v>
       </c>
       <c r="G21" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H21" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
+        <v>45</v>
+      </c>
+      <c r="P21" t="s">
         <v>39</v>
       </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21" t="s">
-        <v>40</v>
-      </c>
-      <c r="R21" t="s">
-        <v>31</v>
-      </c>
-      <c r="S21" t="s">
-        <v>36</v>
-      </c>
-      <c r="T21" t="s">
-        <v>54</v>
-      </c>
-      <c r="U21" t="s">
-        <v>31</v>
-      </c>
-      <c r="X21">
+      <c r="W21" t="s">
+        <v>35</v>
+      </c>
+      <c r="X21" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB21">
         <v>2</v>
       </c>
     </row>
@@ -1155,7 +1239,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -1167,33 +1251,36 @@
         <v>-33</v>
       </c>
       <c r="G22" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H22" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I22" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J22">
         <v>10</v>
       </c>
       <c r="K22" t="s">
-        <v>34</v>
-      </c>
-      <c r="R22" t="s">
-        <v>35</v>
-      </c>
-      <c r="S22" t="s">
-        <v>36</v>
-      </c>
-      <c r="T22" t="s">
-        <v>55</v>
-      </c>
-      <c r="U22" t="s">
-        <v>35</v>
-      </c>
-      <c r="X22">
+        <v>38</v>
+      </c>
+      <c r="P22" t="s">
+        <v>62</v>
+      </c>
+      <c r="W22" t="s">
+        <v>40</v>
+      </c>
+      <c r="X22" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB22">
         <v>2</v>
       </c>
     </row>
@@ -1205,7 +1292,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1217,33 +1304,36 @@
         <v>-43</v>
       </c>
       <c r="G23" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H23" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I23" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J23">
         <v>39</v>
       </c>
       <c r="K23" t="s">
-        <v>34</v>
-      </c>
-      <c r="R23" t="s">
-        <v>35</v>
-      </c>
-      <c r="S23" t="s">
-        <v>36</v>
-      </c>
-      <c r="T23" t="s">
-        <v>56</v>
-      </c>
-      <c r="U23" t="s">
-        <v>31</v>
-      </c>
-      <c r="X23">
+        <v>38</v>
+      </c>
+      <c r="P23" t="s">
+        <v>62</v>
+      </c>
+      <c r="W23" t="s">
+        <v>40</v>
+      </c>
+      <c r="X23" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB23">
         <v>2</v>
       </c>
     </row>
@@ -1255,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1267,33 +1357,36 @@
         <v>18</v>
       </c>
       <c r="G24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H24" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I24" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J24">
         <v>0</v>
       </c>
       <c r="K24" t="s">
-        <v>40</v>
-      </c>
-      <c r="R24" t="s">
-        <v>35</v>
-      </c>
-      <c r="S24" t="s">
-        <v>36</v>
-      </c>
-      <c r="T24" t="s">
-        <v>57</v>
-      </c>
-      <c r="U24" t="s">
-        <v>31</v>
-      </c>
-      <c r="X24">
+        <v>45</v>
+      </c>
+      <c r="P24" t="s">
+        <v>65</v>
+      </c>
+      <c r="W24" t="s">
+        <v>40</v>
+      </c>
+      <c r="X24" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB24">
         <v>2</v>
       </c>
     </row>
@@ -1305,7 +1398,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D25">
         <v>2</v>
@@ -1317,18 +1410,18 @@
         <v>18</v>
       </c>
       <c r="G25" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I25" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J25">
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>40</v>
-      </c>
-      <c r="X25">
+        <v>45</v>
+      </c>
+      <c r="AB25">
         <v>2</v>
       </c>
     </row>
@@ -1340,7 +1433,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -1352,33 +1445,36 @@
         <v>18</v>
       </c>
       <c r="G26" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H26" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I26" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="J26">
         <v>18</v>
       </c>
       <c r="K26" t="s">
-        <v>34</v>
-      </c>
-      <c r="R26" t="s">
-        <v>35</v>
-      </c>
-      <c r="S26" t="s">
-        <v>59</v>
-      </c>
-      <c r="T26" t="s">
-        <v>60</v>
-      </c>
-      <c r="U26" t="s">
-        <v>31</v>
-      </c>
-      <c r="X26">
+        <v>38</v>
+      </c>
+      <c r="P26" t="s">
+        <v>68</v>
+      </c>
+      <c r="W26" t="s">
+        <v>40</v>
+      </c>
+      <c r="X26" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB26">
         <v>2</v>
       </c>
     </row>
@@ -1390,21 +1486,21 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
       <c r="G27" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H27" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I27" t="s">
-        <v>62</v>
-      </c>
-      <c r="X27">
+        <v>72</v>
+      </c>
+      <c r="AB27">
         <v>2</v>
       </c>
     </row>
@@ -1416,19 +1512,19 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F28">
         <v>-40</v>
       </c>
       <c r="G28" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H28" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I28" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29">
@@ -1439,7 +1535,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -1451,33 +1547,36 @@
         <v>-35</v>
       </c>
       <c r="G29" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H29" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I29" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J29">
         <v>3</v>
       </c>
       <c r="K29" t="s">
-        <v>34</v>
-      </c>
-      <c r="R29" t="s">
-        <v>31</v>
-      </c>
-      <c r="S29" t="s">
-        <v>65</v>
-      </c>
-      <c r="U29" t="s">
-        <v>31</v>
-      </c>
-      <c r="V29" t="s">
-        <v>35</v>
-      </c>
-      <c r="X29">
+        <v>38</v>
+      </c>
+      <c r="P29" t="s">
+        <v>54</v>
+      </c>
+      <c r="W29" t="s">
+        <v>35</v>
+      </c>
+      <c r="X29" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB29">
         <v>3</v>
       </c>
     </row>
@@ -1489,7 +1588,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D30">
         <v>2</v>
@@ -1501,33 +1600,36 @@
         <v>-38</v>
       </c>
       <c r="G30" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H30" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I30" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J30">
         <v>3</v>
       </c>
       <c r="K30" t="s">
-        <v>34</v>
-      </c>
-      <c r="R30" t="s">
-        <v>48</v>
-      </c>
-      <c r="S30" t="s">
-        <v>49</v>
-      </c>
-      <c r="U30" t="s">
-        <v>35</v>
-      </c>
-      <c r="V30" t="s">
-        <v>35</v>
-      </c>
-      <c r="X30">
+        <v>38</v>
+      </c>
+      <c r="P30" t="s">
+        <v>54</v>
+      </c>
+      <c r="W30" t="s">
+        <v>55</v>
+      </c>
+      <c r="X30" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB30">
         <v>3</v>
       </c>
     </row>
@@ -1539,7 +1641,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D31">
         <v>3</v>
@@ -1551,30 +1653,33 @@
         <v>-41</v>
       </c>
       <c r="G31" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H31" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I31" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J31">
         <v>2</v>
       </c>
       <c r="K31" t="s">
-        <v>34</v>
-      </c>
-      <c r="R31" t="s">
-        <v>35</v>
-      </c>
-      <c r="U31" t="s">
-        <v>35</v>
-      </c>
-      <c r="V31" t="s">
-        <v>35</v>
-      </c>
-      <c r="X31">
+        <v>38</v>
+      </c>
+      <c r="P31" t="s">
+        <v>54</v>
+      </c>
+      <c r="W31" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB31">
         <v>3</v>
       </c>
     </row>
@@ -1586,7 +1691,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -1598,24 +1703,27 @@
         <v>-43</v>
       </c>
       <c r="G32" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I32" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J32">
         <v>5</v>
       </c>
       <c r="K32" t="s">
-        <v>40</v>
-      </c>
-      <c r="R32" t="s">
-        <v>48</v>
-      </c>
-      <c r="S32" t="s">
-        <v>49</v>
-      </c>
-      <c r="X32">
+        <v>45</v>
+      </c>
+      <c r="P32" t="s">
+        <v>54</v>
+      </c>
+      <c r="W32" t="s">
+        <v>55</v>
+      </c>
+      <c r="X32" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB32">
         <v>3</v>
       </c>
     </row>
@@ -1627,7 +1735,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -1639,15 +1747,15 @@
         <v>-48</v>
       </c>
       <c r="G33" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H33" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I33" t="s">
-        <v>46</v>
-      </c>
-      <c r="X33">
+        <v>52</v>
+      </c>
+      <c r="AB33">
         <v>3</v>
       </c>
     </row>
@@ -1659,7 +1767,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1671,33 +1779,36 @@
         <v>-35</v>
       </c>
       <c r="G34" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H34" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I34" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J34">
         <v>16</v>
       </c>
       <c r="K34" t="s">
-        <v>34</v>
-      </c>
-      <c r="R34" t="s">
-        <v>35</v>
-      </c>
-      <c r="S34" t="s">
-        <v>36</v>
-      </c>
-      <c r="T34" t="s">
-        <v>54</v>
-      </c>
-      <c r="U34" t="s">
-        <v>31</v>
-      </c>
-      <c r="X34">
+        <v>38</v>
+      </c>
+      <c r="P34" t="s">
+        <v>39</v>
+      </c>
+      <c r="W34" t="s">
+        <v>40</v>
+      </c>
+      <c r="X34" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z34" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB34">
         <v>3</v>
       </c>
     </row>
@@ -1709,7 +1820,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1721,33 +1832,36 @@
         <v>49</v>
       </c>
       <c r="G35" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H35" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I35" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="J35">
         <v>-1</v>
       </c>
       <c r="K35" t="s">
-        <v>40</v>
-      </c>
-      <c r="R35" t="s">
-        <v>35</v>
-      </c>
-      <c r="S35" t="s">
-        <v>36</v>
-      </c>
-      <c r="T35" t="s">
-        <v>67</v>
-      </c>
-      <c r="U35" t="s">
-        <v>35</v>
-      </c>
-      <c r="X35">
+        <v>45</v>
+      </c>
+      <c r="P35" t="s">
+        <v>39</v>
+      </c>
+      <c r="W35" t="s">
+        <v>40</v>
+      </c>
+      <c r="X35" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB35">
         <v>3</v>
       </c>
     </row>
@@ -1759,7 +1873,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -1771,30 +1885,33 @@
         <v>48</v>
       </c>
       <c r="G36" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H36" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I36" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K36" t="s">
-        <v>34</v>
-      </c>
-      <c r="R36" t="s">
-        <v>31</v>
-      </c>
-      <c r="S36" t="s">
-        <v>65</v>
-      </c>
-      <c r="U36" t="s">
-        <v>35</v>
-      </c>
-      <c r="V36" t="s">
-        <v>35</v>
-      </c>
-      <c r="X36">
+        <v>38</v>
+      </c>
+      <c r="P36" t="s">
+        <v>54</v>
+      </c>
+      <c r="W36" t="s">
+        <v>35</v>
+      </c>
+      <c r="X36" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA36" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB36">
         <v>4</v>
       </c>
     </row>
@@ -1806,7 +1923,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -1818,33 +1935,36 @@
         <v>33</v>
       </c>
       <c r="G37" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H37" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I37" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37" t="s">
-        <v>34</v>
-      </c>
-      <c r="R37" t="s">
-        <v>48</v>
-      </c>
-      <c r="S37" t="s">
-        <v>49</v>
-      </c>
-      <c r="U37" t="s">
-        <v>31</v>
-      </c>
-      <c r="V37" t="s">
-        <v>31</v>
-      </c>
-      <c r="X37">
+        <v>38</v>
+      </c>
+      <c r="P37" t="s">
+        <v>54</v>
+      </c>
+      <c r="W37" t="s">
+        <v>55</v>
+      </c>
+      <c r="X37" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB37">
         <v>4</v>
       </c>
     </row>
@@ -1856,7 +1976,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D38">
         <v>2</v>
@@ -1868,30 +1988,33 @@
         <v>33</v>
       </c>
       <c r="G38" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H38" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I38" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J38">
         <v>4</v>
       </c>
       <c r="K38" t="s">
-        <v>34</v>
-      </c>
-      <c r="R38" t="s">
-        <v>35</v>
-      </c>
-      <c r="U38" t="s">
-        <v>35</v>
-      </c>
-      <c r="V38" t="s">
-        <v>35</v>
-      </c>
-      <c r="X38">
+        <v>38</v>
+      </c>
+      <c r="P38" t="s">
+        <v>54</v>
+      </c>
+      <c r="W38" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA38" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB38">
         <v>4</v>
       </c>
     </row>
@@ -1903,7 +2026,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -1915,30 +2038,33 @@
         <v>29</v>
       </c>
       <c r="G39" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H39" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I39" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J39">
         <v>2</v>
       </c>
       <c r="K39" t="s">
-        <v>34</v>
-      </c>
-      <c r="R39" t="s">
-        <v>31</v>
-      </c>
-      <c r="S39" t="s">
-        <v>50</v>
-      </c>
-      <c r="U39" t="s">
-        <v>31</v>
-      </c>
-      <c r="X39">
+        <v>38</v>
+      </c>
+      <c r="P39" t="s">
+        <v>54</v>
+      </c>
+      <c r="W39" t="s">
+        <v>35</v>
+      </c>
+      <c r="X39" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB39">
         <v>4</v>
       </c>
     </row>
@@ -1950,7 +2076,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -1962,27 +2088,30 @@
         <v>27</v>
       </c>
       <c r="G40" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H40" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I40" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K40" t="s">
-        <v>34</v>
-      </c>
-      <c r="R40" t="s">
-        <v>35</v>
-      </c>
-      <c r="S40" t="s">
-        <v>50</v>
-      </c>
-      <c r="U40" t="s">
-        <v>35</v>
-      </c>
-      <c r="X40">
+        <v>38</v>
+      </c>
+      <c r="P40" t="s">
+        <v>54</v>
+      </c>
+      <c r="W40" t="s">
+        <v>40</v>
+      </c>
+      <c r="X40" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB40">
         <v>4</v>
       </c>
     </row>
@@ -1994,7 +2123,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2006,33 +2135,36 @@
         <v>-23</v>
       </c>
       <c r="G41" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H41" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I41" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J41">
         <v>6</v>
       </c>
       <c r="K41" t="s">
-        <v>34</v>
-      </c>
-      <c r="R41" t="s">
-        <v>35</v>
-      </c>
-      <c r="S41" t="s">
-        <v>36</v>
-      </c>
-      <c r="T41" t="s">
-        <v>54</v>
-      </c>
-      <c r="U41" t="s">
-        <v>31</v>
-      </c>
-      <c r="X41">
+        <v>38</v>
+      </c>
+      <c r="P41" t="s">
+        <v>39</v>
+      </c>
+      <c r="W41" t="s">
+        <v>40</v>
+      </c>
+      <c r="X41" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB41">
         <v>4</v>
       </c>
     </row>
@@ -2044,7 +2176,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D42">
         <v>2</v>
@@ -2056,33 +2188,36 @@
         <v>-29</v>
       </c>
       <c r="G42" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H42" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I42" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J42">
         <v>31</v>
       </c>
       <c r="K42" t="s">
-        <v>34</v>
-      </c>
-      <c r="R42" t="s">
-        <v>35</v>
-      </c>
-      <c r="S42" t="s">
-        <v>36</v>
-      </c>
-      <c r="T42" t="s">
-        <v>54</v>
-      </c>
-      <c r="U42" t="s">
-        <v>31</v>
-      </c>
-      <c r="X42">
+        <v>38</v>
+      </c>
+      <c r="P42" t="s">
+        <v>39</v>
+      </c>
+      <c r="W42" t="s">
+        <v>40</v>
+      </c>
+      <c r="X42" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB42">
         <v>4</v>
       </c>
     </row>
@@ -2094,7 +2229,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2106,33 +2241,36 @@
         <v>40</v>
       </c>
       <c r="G43" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H43" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I43" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J43">
         <v>-1</v>
       </c>
       <c r="K43" t="s">
-        <v>40</v>
-      </c>
-      <c r="R43" t="s">
-        <v>35</v>
-      </c>
-      <c r="S43" t="s">
-        <v>36</v>
-      </c>
-      <c r="T43" t="s">
-        <v>56</v>
-      </c>
-      <c r="U43" t="s">
-        <v>35</v>
-      </c>
-      <c r="X43">
+        <v>45</v>
+      </c>
+      <c r="P43" t="s">
+        <v>62</v>
+      </c>
+      <c r="W43" t="s">
+        <v>40</v>
+      </c>
+      <c r="X43" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y43" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z43" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB43">
         <v>4</v>
       </c>
     </row>
@@ -2144,7 +2282,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -2156,33 +2294,36 @@
         <v>41</v>
       </c>
       <c r="G44" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H44" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I44" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J44">
         <v>4</v>
       </c>
       <c r="K44" t="s">
-        <v>40</v>
-      </c>
-      <c r="R44" t="s">
-        <v>31</v>
-      </c>
-      <c r="S44" t="s">
-        <v>36</v>
-      </c>
-      <c r="T44" t="s">
-        <v>69</v>
-      </c>
-      <c r="U44" t="s">
-        <v>31</v>
-      </c>
-      <c r="X44">
+        <v>45</v>
+      </c>
+      <c r="P44" t="s">
+        <v>39</v>
+      </c>
+      <c r="W44" t="s">
+        <v>35</v>
+      </c>
+      <c r="X44" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y44" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB44">
         <v>4</v>
       </c>
     </row>
@@ -2194,7 +2335,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D45">
         <v>3</v>
@@ -2206,24 +2347,27 @@
         <v>37</v>
       </c>
       <c r="G45" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I45" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J45">
         <v>5</v>
       </c>
       <c r="K45" t="s">
-        <v>40</v>
-      </c>
-      <c r="R45" t="s">
-        <v>35</v>
-      </c>
-      <c r="S45" t="s">
-        <v>70</v>
-      </c>
-      <c r="X45">
+        <v>45</v>
+      </c>
+      <c r="P45" t="s">
+        <v>68</v>
+      </c>
+      <c r="W45" t="s">
+        <v>40</v>
+      </c>
+      <c r="X45" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB45">
         <v>4</v>
       </c>
     </row>
@@ -2235,7 +2379,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D46">
         <v>3</v>
@@ -2247,33 +2391,36 @@
         <v>32</v>
       </c>
       <c r="G46" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H46" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I46" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J46">
         <v>12</v>
       </c>
       <c r="K46" t="s">
-        <v>34</v>
-      </c>
-      <c r="R46" t="s">
-        <v>35</v>
-      </c>
-      <c r="S46" t="s">
-        <v>70</v>
-      </c>
-      <c r="T46" t="s">
-        <v>56</v>
-      </c>
-      <c r="U46" t="s">
-        <v>31</v>
-      </c>
-      <c r="X46">
+        <v>38</v>
+      </c>
+      <c r="P46" t="s">
+        <v>68</v>
+      </c>
+      <c r="W46" t="s">
+        <v>40</v>
+      </c>
+      <c r="X46" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB46">
         <v>4</v>
       </c>
     </row>
@@ -2285,7 +2432,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2297,33 +2444,36 @@
         <v>20</v>
       </c>
       <c r="G47" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H47" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I47" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J47">
         <v>7</v>
       </c>
       <c r="K47" t="s">
-        <v>34</v>
-      </c>
-      <c r="R47" t="s">
-        <v>35</v>
-      </c>
-      <c r="S47" t="s">
-        <v>70</v>
-      </c>
-      <c r="T47" t="s">
-        <v>71</v>
-      </c>
-      <c r="U47" t="s">
-        <v>35</v>
-      </c>
-      <c r="X47">
+        <v>38</v>
+      </c>
+      <c r="P47" t="s">
+        <v>68</v>
+      </c>
+      <c r="W47" t="s">
+        <v>40</v>
+      </c>
+      <c r="X47" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y47" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB47">
         <v>4</v>
       </c>
     </row>
@@ -2335,7 +2485,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D48">
         <v>2</v>
@@ -2347,33 +2497,36 @@
         <v>13</v>
       </c>
       <c r="G48" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H48" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I48" t="s">
+        <v>44</v>
+      </c>
+      <c r="J48">
+        <v>3</v>
+      </c>
+      <c r="K48" t="s">
+        <v>38</v>
+      </c>
+      <c r="P48" t="s">
         <v>39</v>
       </c>
-      <c r="J48">
-        <v>3</v>
-      </c>
-      <c r="K48" t="s">
-        <v>34</v>
-      </c>
-      <c r="R48" t="s">
-        <v>31</v>
-      </c>
-      <c r="S48" t="s">
-        <v>36</v>
-      </c>
-      <c r="T48" t="s">
-        <v>54</v>
-      </c>
-      <c r="U48" t="s">
-        <v>31</v>
-      </c>
-      <c r="X48">
+      <c r="W48" t="s">
+        <v>35</v>
+      </c>
+      <c r="X48" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB48">
         <v>4</v>
       </c>
     </row>
@@ -2385,7 +2538,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2397,33 +2550,36 @@
         <v>10</v>
       </c>
       <c r="G49" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H49" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I49" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="J49">
         <v>10</v>
       </c>
       <c r="K49" t="s">
-        <v>34</v>
-      </c>
-      <c r="R49" t="s">
-        <v>31</v>
-      </c>
-      <c r="S49" t="s">
-        <v>36</v>
-      </c>
-      <c r="T49" t="s">
-        <v>73</v>
-      </c>
-      <c r="U49" t="s">
-        <v>35</v>
-      </c>
-      <c r="X49">
+        <v>38</v>
+      </c>
+      <c r="P49" t="s">
+        <v>48</v>
+      </c>
+      <c r="W49" t="s">
+        <v>35</v>
+      </c>
+      <c r="X49" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y49" t="s">
+        <v>83</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB49">
         <v>4</v>
       </c>
     </row>
@@ -2435,21 +2591,21 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F50">
         <v>3</v>
       </c>
       <c r="G50" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H50" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I50" t="s">
-        <v>62</v>
-      </c>
-      <c r="X50">
+        <v>72</v>
+      </c>
+      <c r="AB50">
         <v>4</v>
       </c>
     </row>
@@ -2461,19 +2617,19 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F51">
         <v>-40</v>
       </c>
       <c r="G51" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H51" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I51" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52">
@@ -2484,7 +2640,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2496,33 +2652,36 @@
         <v>-4</v>
       </c>
       <c r="G52" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H52" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I52" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J52">
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>34</v>
-      </c>
-      <c r="R52" t="s">
-        <v>31</v>
-      </c>
-      <c r="S52" t="s">
-        <v>65</v>
-      </c>
-      <c r="U52" t="s">
-        <v>35</v>
-      </c>
-      <c r="V52" t="s">
-        <v>35</v>
-      </c>
-      <c r="X52">
+        <v>38</v>
+      </c>
+      <c r="P52" t="s">
+        <v>54</v>
+      </c>
+      <c r="W52" t="s">
+        <v>35</v>
+      </c>
+      <c r="X52" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z52" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA52" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB52">
         <v>5</v>
       </c>
     </row>
@@ -2534,19 +2693,19 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F53">
         <v>-20</v>
       </c>
       <c r="G53" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H53" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I53" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54">
@@ -2557,7 +2716,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2569,33 +2728,36 @@
         <v>-35</v>
       </c>
       <c r="G54" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H54" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I54" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J54">
         <v>21</v>
       </c>
       <c r="K54" t="s">
-        <v>34</v>
-      </c>
-      <c r="R54" t="s">
-        <v>31</v>
-      </c>
-      <c r="S54" t="s">
-        <v>75</v>
-      </c>
-      <c r="T54" t="s">
-        <v>76</v>
-      </c>
-      <c r="U54" t="s">
-        <v>35</v>
-      </c>
-      <c r="X54">
+        <v>38</v>
+      </c>
+      <c r="P54" t="s">
+        <v>68</v>
+      </c>
+      <c r="W54" t="s">
+        <v>35</v>
+      </c>
+      <c r="X54" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB54">
         <v>5</v>
       </c>
     </row>
@@ -2607,7 +2769,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2619,33 +2781,36 @@
         <v>44</v>
       </c>
       <c r="G55" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H55" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I55" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J55">
         <v>0</v>
       </c>
       <c r="K55" t="s">
-        <v>40</v>
-      </c>
-      <c r="R55" t="s">
-        <v>35</v>
-      </c>
-      <c r="S55" t="s">
-        <v>41</v>
-      </c>
-      <c r="T55" t="s">
-        <v>77</v>
-      </c>
-      <c r="U55" t="s">
-        <v>35</v>
-      </c>
-      <c r="X55">
+        <v>45</v>
+      </c>
+      <c r="P55" t="s">
+        <v>39</v>
+      </c>
+      <c r="W55" t="s">
+        <v>40</v>
+      </c>
+      <c r="X55" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB55">
         <v>5</v>
       </c>
     </row>
@@ -2657,7 +2822,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -2669,33 +2834,36 @@
         <v>44</v>
       </c>
       <c r="G56" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H56" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I56" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J56">
         <v>9</v>
       </c>
       <c r="K56" t="s">
-        <v>34</v>
-      </c>
-      <c r="R56" t="s">
-        <v>31</v>
-      </c>
-      <c r="S56" t="s">
-        <v>36</v>
-      </c>
-      <c r="T56" t="s">
-        <v>42</v>
-      </c>
-      <c r="U56" t="s">
-        <v>35</v>
-      </c>
-      <c r="X56">
+        <v>38</v>
+      </c>
+      <c r="P56" t="s">
+        <v>39</v>
+      </c>
+      <c r="W56" t="s">
+        <v>35</v>
+      </c>
+      <c r="X56" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB56">
         <v>5</v>
       </c>
     </row>
@@ -2707,7 +2875,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D57">
         <v>3</v>
@@ -2719,33 +2887,36 @@
         <v>35</v>
       </c>
       <c r="G57" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H57" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I57" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J57">
         <v>2</v>
       </c>
       <c r="K57" t="s">
-        <v>34</v>
-      </c>
-      <c r="R57" t="s">
-        <v>31</v>
-      </c>
-      <c r="S57" t="s">
-        <v>78</v>
-      </c>
-      <c r="T57" t="s">
-        <v>79</v>
-      </c>
-      <c r="U57" t="s">
-        <v>35</v>
-      </c>
-      <c r="X57">
+        <v>38</v>
+      </c>
+      <c r="P57" t="s">
+        <v>88</v>
+      </c>
+      <c r="W57" t="s">
+        <v>35</v>
+      </c>
+      <c r="X57" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB57">
         <v>5</v>
       </c>
     </row>
@@ -2757,7 +2928,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2769,33 +2940,36 @@
         <v>33</v>
       </c>
       <c r="G58" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H58" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I58" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="J58">
         <v>33</v>
       </c>
       <c r="K58" t="s">
-        <v>34</v>
-      </c>
-      <c r="R58" t="s">
-        <v>31</v>
-      </c>
-      <c r="S58" t="s">
-        <v>36</v>
-      </c>
-      <c r="T58" t="s">
-        <v>80</v>
-      </c>
-      <c r="U58" t="s">
-        <v>31</v>
-      </c>
-      <c r="X58">
+        <v>38</v>
+      </c>
+      <c r="P58" t="s">
+        <v>39</v>
+      </c>
+      <c r="W58" t="s">
+        <v>35</v>
+      </c>
+      <c r="X58" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB58">
         <v>5</v>
       </c>
     </row>
@@ -2807,21 +2981,21 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F59">
         <v>3</v>
       </c>
       <c r="G59" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H59" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I59" t="s">
-        <v>62</v>
-      </c>
-      <c r="X59">
+        <v>72</v>
+      </c>
+      <c r="AB59">
         <v>5</v>
       </c>
     </row>
@@ -2833,19 +3007,19 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F60">
         <v>-40</v>
       </c>
       <c r="G60" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H60" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I60" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="61">
@@ -2856,7 +3030,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2868,33 +3042,36 @@
         <v>-35</v>
       </c>
       <c r="G61" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H61" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I61" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J61">
         <v>14</v>
       </c>
       <c r="K61" t="s">
-        <v>40</v>
-      </c>
-      <c r="R61" t="s">
-        <v>48</v>
-      </c>
-      <c r="S61" t="s">
-        <v>49</v>
-      </c>
-      <c r="U61" t="s">
-        <v>31</v>
-      </c>
-      <c r="V61" t="s">
-        <v>35</v>
-      </c>
-      <c r="X61">
+        <v>45</v>
+      </c>
+      <c r="P61" t="s">
+        <v>54</v>
+      </c>
+      <c r="W61" t="s">
+        <v>55</v>
+      </c>
+      <c r="X61" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA61" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB61">
         <v>5</v>
       </c>
     </row>
@@ -2906,7 +3083,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2918,30 +3095,33 @@
         <v>-49</v>
       </c>
       <c r="G62" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H62" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I62" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J62">
         <v>-3</v>
       </c>
       <c r="K62" t="s">
-        <v>34</v>
-      </c>
-      <c r="R62" t="s">
-        <v>48</v>
-      </c>
-      <c r="S62" t="s">
-        <v>49</v>
-      </c>
-      <c r="U62" t="s">
-        <v>35</v>
-      </c>
-      <c r="X62">
+        <v>38</v>
+      </c>
+      <c r="P62" t="s">
+        <v>54</v>
+      </c>
+      <c r="W62" t="s">
+        <v>55</v>
+      </c>
+      <c r="X62" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB62">
         <v>5</v>
       </c>
     </row>
@@ -2953,7 +3133,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -2965,33 +3145,36 @@
         <v>-46</v>
       </c>
       <c r="G63" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H63" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I63" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J63">
         <v>6</v>
       </c>
       <c r="K63" t="s">
-        <v>34</v>
-      </c>
-      <c r="R63" t="s">
-        <v>31</v>
-      </c>
-      <c r="S63" t="s">
-        <v>65</v>
-      </c>
-      <c r="U63" t="s">
-        <v>31</v>
-      </c>
-      <c r="V63" t="s">
-        <v>35</v>
-      </c>
-      <c r="X63">
+        <v>38</v>
+      </c>
+      <c r="P63" t="s">
+        <v>54</v>
+      </c>
+      <c r="W63" t="s">
+        <v>35</v>
+      </c>
+      <c r="X63" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB63">
         <v>5</v>
       </c>
     </row>
@@ -3003,7 +3186,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D64">
         <v>3</v>
@@ -3015,30 +3198,33 @@
         <v>48</v>
       </c>
       <c r="G64" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H64" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I64" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K64" t="s">
-        <v>34</v>
-      </c>
-      <c r="R64" t="s">
-        <v>31</v>
-      </c>
-      <c r="S64" t="s">
-        <v>65</v>
-      </c>
-      <c r="U64" t="s">
-        <v>35</v>
-      </c>
-      <c r="V64" t="s">
-        <v>35</v>
-      </c>
-      <c r="X64">
+        <v>38</v>
+      </c>
+      <c r="P64" t="s">
+        <v>54</v>
+      </c>
+      <c r="W64" t="s">
+        <v>35</v>
+      </c>
+      <c r="X64" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA64" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB64">
         <v>5</v>
       </c>
     </row>
@@ -3050,7 +3236,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3062,33 +3248,36 @@
         <v>49</v>
       </c>
       <c r="G65" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H65" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I65" t="s">
+        <v>44</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="K65" t="s">
+        <v>45</v>
+      </c>
+      <c r="P65" t="s">
         <v>39</v>
       </c>
-      <c r="J65">
-        <v>1</v>
-      </c>
-      <c r="K65" t="s">
-        <v>40</v>
-      </c>
-      <c r="R65" t="s">
-        <v>35</v>
-      </c>
-      <c r="S65" t="s">
-        <v>36</v>
-      </c>
-      <c r="T65" t="s">
-        <v>76</v>
-      </c>
-      <c r="U65" t="s">
-        <v>31</v>
-      </c>
-      <c r="X65">
+      <c r="W65" t="s">
+        <v>40</v>
+      </c>
+      <c r="X65" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB65">
         <v>6</v>
       </c>
     </row>
@@ -3100,7 +3289,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D66">
         <v>2</v>
@@ -3112,33 +3301,36 @@
         <v>48</v>
       </c>
       <c r="G66" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H66" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I66" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J66">
         <v>14</v>
       </c>
       <c r="K66" t="s">
-        <v>34</v>
-      </c>
-      <c r="R66" t="s">
-        <v>35</v>
-      </c>
-      <c r="S66" t="s">
-        <v>59</v>
-      </c>
-      <c r="T66" t="s">
-        <v>37</v>
-      </c>
-      <c r="U66" t="s">
-        <v>31</v>
-      </c>
-      <c r="X66">
+        <v>38</v>
+      </c>
+      <c r="P66" t="s">
+        <v>68</v>
+      </c>
+      <c r="W66" t="s">
+        <v>40</v>
+      </c>
+      <c r="X66" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB66">
         <v>6</v>
       </c>
     </row>
@@ -3150,7 +3342,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3162,33 +3354,36 @@
         <v>34</v>
       </c>
       <c r="G67" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H67" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I67" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="J67">
         <v>34</v>
       </c>
       <c r="K67" t="s">
-        <v>34</v>
-      </c>
-      <c r="R67" t="s">
-        <v>35</v>
-      </c>
-      <c r="S67" t="s">
-        <v>36</v>
-      </c>
-      <c r="T67" t="s">
-        <v>81</v>
-      </c>
-      <c r="U67" t="s">
-        <v>35</v>
-      </c>
-      <c r="X67">
+        <v>38</v>
+      </c>
+      <c r="P67" t="s">
+        <v>62</v>
+      </c>
+      <c r="W67" t="s">
+        <v>40</v>
+      </c>
+      <c r="X67" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB67">
         <v>6</v>
       </c>
     </row>
@@ -3200,21 +3395,21 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F68">
         <v>3</v>
       </c>
       <c r="G68" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H68" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I68" t="s">
-        <v>82</v>
-      </c>
-      <c r="X68">
+        <v>93</v>
+      </c>
+      <c r="AB68">
         <v>6</v>
       </c>
     </row>
@@ -3226,19 +3421,19 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F69">
         <v>-40</v>
       </c>
       <c r="G69" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H69" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I69" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="70">
@@ -3249,7 +3444,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3261,33 +3456,36 @@
         <v>-35</v>
       </c>
       <c r="G70" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H70" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I70" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J70">
         <v>-3</v>
       </c>
       <c r="K70" t="s">
-        <v>34</v>
-      </c>
-      <c r="R70" t="s">
-        <v>31</v>
-      </c>
-      <c r="S70" t="s">
-        <v>65</v>
-      </c>
-      <c r="U70" t="s">
-        <v>35</v>
-      </c>
-      <c r="V70" t="s">
-        <v>31</v>
-      </c>
-      <c r="X70">
+        <v>38</v>
+      </c>
+      <c r="P70" t="s">
+        <v>54</v>
+      </c>
+      <c r="W70" t="s">
+        <v>35</v>
+      </c>
+      <c r="X70" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB70">
         <v>6</v>
       </c>
     </row>
@@ -3299,7 +3497,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D71">
         <v>2</v>
@@ -3311,33 +3509,36 @@
         <v>-32</v>
       </c>
       <c r="G71" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H71" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I71" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J71">
         <v>10</v>
       </c>
       <c r="K71" t="s">
-        <v>40</v>
-      </c>
-      <c r="R71" t="s">
-        <v>48</v>
-      </c>
-      <c r="S71" t="s">
-        <v>49</v>
-      </c>
-      <c r="U71" t="s">
-        <v>35</v>
-      </c>
-      <c r="V71" t="s">
-        <v>35</v>
-      </c>
-      <c r="X71">
+        <v>45</v>
+      </c>
+      <c r="P71" t="s">
+        <v>54</v>
+      </c>
+      <c r="W71" t="s">
+        <v>55</v>
+      </c>
+      <c r="X71" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA71" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB71">
         <v>6</v>
       </c>
     </row>
@@ -3349,7 +3550,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D72">
         <v>3</v>
@@ -3361,33 +3562,36 @@
         <v>-42</v>
       </c>
       <c r="G72" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H72" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I72" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J72">
         <v>-9</v>
       </c>
       <c r="K72" t="s">
-        <v>34</v>
-      </c>
-      <c r="R72" t="s">
-        <v>48</v>
-      </c>
-      <c r="S72" t="s">
-        <v>49</v>
-      </c>
-      <c r="U72" t="s">
-        <v>31</v>
-      </c>
-      <c r="V72" t="s">
-        <v>31</v>
-      </c>
-      <c r="X72">
+        <v>38</v>
+      </c>
+      <c r="P72" t="s">
+        <v>54</v>
+      </c>
+      <c r="W72" t="s">
+        <v>55</v>
+      </c>
+      <c r="X72" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z72" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA72" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB72">
         <v>6</v>
       </c>
     </row>
@@ -3399,7 +3603,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D73">
         <v>4</v>
@@ -3411,15 +3615,15 @@
         <v>-33</v>
       </c>
       <c r="G73" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H73" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I73" t="s">
-        <v>29</v>
-      </c>
-      <c r="X73">
+        <v>33</v>
+      </c>
+      <c r="AB73">
         <v>6</v>
       </c>
     </row>
@@ -3431,7 +3635,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3443,33 +3647,36 @@
         <v>20</v>
       </c>
       <c r="G74" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H74" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I74" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="J74">
         <v>20</v>
       </c>
       <c r="K74" t="s">
-        <v>34</v>
-      </c>
-      <c r="R74" t="s">
-        <v>35</v>
-      </c>
-      <c r="S74" t="s">
-        <v>70</v>
-      </c>
-      <c r="T74" t="s">
-        <v>83</v>
-      </c>
-      <c r="U74" t="s">
-        <v>31</v>
-      </c>
-      <c r="X74">
+        <v>38</v>
+      </c>
+      <c r="P74" t="s">
+        <v>68</v>
+      </c>
+      <c r="W74" t="s">
+        <v>40</v>
+      </c>
+      <c r="X74" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>94</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB74">
         <v>7</v>
       </c>
     </row>
@@ -3481,21 +3688,21 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F75">
         <v>3</v>
       </c>
       <c r="G75" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H75" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I75" t="s">
-        <v>62</v>
-      </c>
-      <c r="X75">
+        <v>72</v>
+      </c>
+      <c r="AB75">
         <v>7</v>
       </c>
     </row>
@@ -3507,19 +3714,19 @@
         <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F76">
         <v>-40</v>
       </c>
       <c r="G76" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H76" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I76" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="77">
@@ -3530,7 +3737,7 @@
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3542,33 +3749,36 @@
         <v>-48</v>
       </c>
       <c r="G77" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H77" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I77" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J77">
         <v>7</v>
       </c>
       <c r="K77" t="s">
-        <v>40</v>
-      </c>
-      <c r="R77" t="s">
-        <v>31</v>
-      </c>
-      <c r="S77" t="s">
-        <v>65</v>
-      </c>
-      <c r="U77" t="s">
-        <v>31</v>
-      </c>
-      <c r="V77" t="s">
-        <v>31</v>
-      </c>
-      <c r="X77">
+        <v>45</v>
+      </c>
+      <c r="P77" t="s">
+        <v>54</v>
+      </c>
+      <c r="W77" t="s">
+        <v>35</v>
+      </c>
+      <c r="X77" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA77" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB77">
         <v>7</v>
       </c>
     </row>
@@ -3580,7 +3790,7 @@
         <v>2</v>
       </c>
       <c r="C78" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -3592,33 +3802,36 @@
         <v>45</v>
       </c>
       <c r="G78" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H78" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I78" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J78">
         <v>2</v>
       </c>
       <c r="K78" t="s">
-        <v>40</v>
-      </c>
-      <c r="R78" t="s">
-        <v>35</v>
-      </c>
-      <c r="S78" t="s">
-        <v>65</v>
-      </c>
-      <c r="U78" t="s">
-        <v>35</v>
-      </c>
-      <c r="V78" t="s">
-        <v>35</v>
-      </c>
-      <c r="X78">
+        <v>45</v>
+      </c>
+      <c r="P78" t="s">
+        <v>54</v>
+      </c>
+      <c r="W78" t="s">
+        <v>40</v>
+      </c>
+      <c r="X78" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA78" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB78">
         <v>7</v>
       </c>
     </row>
@@ -3630,7 +3843,7 @@
         <v>2</v>
       </c>
       <c r="C79" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D79">
         <v>3</v>
@@ -3642,33 +3855,36 @@
         <v>43</v>
       </c>
       <c r="G79" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H79" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I79" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J79">
         <v>0</v>
       </c>
       <c r="K79" t="s">
-        <v>34</v>
-      </c>
-      <c r="R79" t="s">
-        <v>48</v>
-      </c>
-      <c r="S79" t="s">
-        <v>49</v>
-      </c>
-      <c r="U79" t="s">
-        <v>35</v>
-      </c>
-      <c r="V79" t="s">
-        <v>31</v>
-      </c>
-      <c r="X79">
+        <v>38</v>
+      </c>
+      <c r="P79" t="s">
+        <v>54</v>
+      </c>
+      <c r="W79" t="s">
+        <v>55</v>
+      </c>
+      <c r="X79" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB79">
         <v>7</v>
       </c>
     </row>
@@ -3680,21 +3896,21 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F80">
         <v>-40</v>
       </c>
       <c r="G80" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H80" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I80" t="s">
-        <v>29</v>
-      </c>
-      <c r="X80">
+        <v>33</v>
+      </c>
+      <c r="AB80">
         <v>7</v>
       </c>
     </row>
@@ -3706,7 +3922,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -3718,33 +3934,36 @@
         <v>-23</v>
       </c>
       <c r="G81" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H81" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I81" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J81">
         <v>4</v>
       </c>
       <c r="K81" t="s">
-        <v>40</v>
-      </c>
-      <c r="R81" t="s">
-        <v>48</v>
-      </c>
-      <c r="S81" t="s">
-        <v>49</v>
-      </c>
-      <c r="U81" t="s">
-        <v>31</v>
-      </c>
-      <c r="V81" t="s">
-        <v>35</v>
-      </c>
-      <c r="X81">
+        <v>45</v>
+      </c>
+      <c r="P81" t="s">
+        <v>54</v>
+      </c>
+      <c r="W81" t="s">
+        <v>55</v>
+      </c>
+      <c r="X81" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA81" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB81">
         <v>8</v>
       </c>
     </row>
@@ -3756,7 +3975,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D82">
         <v>2</v>
@@ -3768,21 +3987,21 @@
         <v>-27</v>
       </c>
       <c r="G82" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I82" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>34</v>
-      </c>
-      <c r="R82" t="s">
-        <v>48</v>
-      </c>
-      <c r="X82">
+        <v>38</v>
+      </c>
+      <c r="W82" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB82">
         <v>8</v>
       </c>
     </row>
@@ -3794,7 +4013,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -3806,33 +4025,36 @@
         <v>-27</v>
       </c>
       <c r="G83" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H83" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I83" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J83">
         <v>11</v>
       </c>
       <c r="K83" t="s">
-        <v>40</v>
-      </c>
-      <c r="R83" t="s">
-        <v>31</v>
-      </c>
-      <c r="S83" t="s">
-        <v>65</v>
-      </c>
-      <c r="U83" t="s">
-        <v>31</v>
-      </c>
-      <c r="V83" t="s">
-        <v>31</v>
-      </c>
-      <c r="X83">
+        <v>45</v>
+      </c>
+      <c r="P83" t="s">
+        <v>54</v>
+      </c>
+      <c r="W83" t="s">
+        <v>35</v>
+      </c>
+      <c r="X83" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA83" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB83">
         <v>8</v>
       </c>
     </row>
@@ -3844,7 +4066,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3856,30 +4078,33 @@
         <v>-38</v>
       </c>
       <c r="G84" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H84" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I84" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J84">
         <v>-10</v>
       </c>
       <c r="K84" t="s">
-        <v>34</v>
-      </c>
-      <c r="R84" t="s">
-        <v>35</v>
-      </c>
-      <c r="U84" t="s">
-        <v>35</v>
-      </c>
-      <c r="V84" t="s">
-        <v>35</v>
-      </c>
-      <c r="X84">
+        <v>38</v>
+      </c>
+      <c r="P84" t="s">
+        <v>54</v>
+      </c>
+      <c r="W84" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA84" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB84">
         <v>8</v>
       </c>
     </row>
@@ -3891,7 +4116,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3903,30 +4128,33 @@
         <v>-28</v>
       </c>
       <c r="G85" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H85" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I85" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J85">
         <v>6</v>
       </c>
       <c r="K85" t="s">
-        <v>34</v>
-      </c>
-      <c r="R85" t="s">
-        <v>31</v>
-      </c>
-      <c r="U85" t="s">
-        <v>31</v>
-      </c>
-      <c r="V85" t="s">
-        <v>31</v>
-      </c>
-      <c r="X85">
+        <v>38</v>
+      </c>
+      <c r="P85" t="s">
+        <v>54</v>
+      </c>
+      <c r="W85" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA85" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB85">
         <v>8</v>
       </c>
     </row>
@@ -3938,7 +4166,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D86">
         <v>2</v>
@@ -3950,33 +4178,36 @@
         <v>-34</v>
       </c>
       <c r="G86" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H86" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I86" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J86">
         <v>0</v>
       </c>
       <c r="K86" t="s">
-        <v>34</v>
-      </c>
-      <c r="R86" t="s">
-        <v>48</v>
-      </c>
-      <c r="S86" t="s">
-        <v>49</v>
-      </c>
-      <c r="U86" t="s">
-        <v>31</v>
-      </c>
-      <c r="V86" t="s">
-        <v>31</v>
-      </c>
-      <c r="X86">
+        <v>38</v>
+      </c>
+      <c r="P86" t="s">
+        <v>54</v>
+      </c>
+      <c r="W86" t="s">
+        <v>55</v>
+      </c>
+      <c r="X86" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA86" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB86">
         <v>8</v>
       </c>
     </row>
@@ -3988,7 +4219,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D87">
         <v>3</v>
@@ -4000,33 +4231,36 @@
         <v>-34</v>
       </c>
       <c r="G87" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H87" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I87" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J87">
         <v>-9</v>
       </c>
       <c r="K87" t="s">
-        <v>34</v>
-      </c>
-      <c r="R87" t="s">
-        <v>48</v>
-      </c>
-      <c r="S87" t="s">
-        <v>49</v>
-      </c>
-      <c r="U87" t="s">
-        <v>35</v>
-      </c>
-      <c r="V87" t="s">
-        <v>31</v>
-      </c>
-      <c r="X87">
+        <v>38</v>
+      </c>
+      <c r="P87" t="s">
+        <v>54</v>
+      </c>
+      <c r="W87" t="s">
+        <v>55</v>
+      </c>
+      <c r="X87" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z87" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA87" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB87">
         <v>8</v>
       </c>
     </row>
@@ -4038,7 +4272,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D88">
         <v>4</v>
@@ -4050,15 +4284,15 @@
         <v>-25</v>
       </c>
       <c r="G88" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H88" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I88" t="s">
-        <v>29</v>
-      </c>
-      <c r="X88">
+        <v>33</v>
+      </c>
+      <c r="AB88">
         <v>8</v>
       </c>
     </row>
@@ -4070,7 +4304,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -4082,33 +4316,36 @@
         <v>-46</v>
       </c>
       <c r="G89" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H89" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I89" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J89">
         <v>22</v>
       </c>
       <c r="K89" t="s">
-        <v>34</v>
-      </c>
-      <c r="R89" t="s">
-        <v>31</v>
-      </c>
-      <c r="S89" t="s">
-        <v>70</v>
-      </c>
-      <c r="T89" t="s">
-        <v>56</v>
-      </c>
-      <c r="U89" t="s">
-        <v>35</v>
-      </c>
-      <c r="X89">
+        <v>38</v>
+      </c>
+      <c r="P89" t="s">
+        <v>68</v>
+      </c>
+      <c r="W89" t="s">
+        <v>35</v>
+      </c>
+      <c r="X89" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB89">
         <v>8</v>
       </c>
     </row>
@@ -4120,7 +4357,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -4132,33 +4369,36 @@
         <v>32</v>
       </c>
       <c r="G90" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H90" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I90" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J90">
         <v>5</v>
       </c>
       <c r="K90" t="s">
-        <v>34</v>
-      </c>
-      <c r="R90" t="s">
-        <v>31</v>
-      </c>
-      <c r="S90" t="s">
-        <v>70</v>
-      </c>
-      <c r="T90" t="s">
-        <v>57</v>
-      </c>
-      <c r="U90" t="s">
-        <v>35</v>
-      </c>
-      <c r="X90">
+        <v>38</v>
+      </c>
+      <c r="P90" t="s">
+        <v>68</v>
+      </c>
+      <c r="W90" t="s">
+        <v>35</v>
+      </c>
+      <c r="X90" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB90">
         <v>8</v>
       </c>
     </row>
@@ -4170,7 +4410,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D91">
         <v>2</v>
@@ -4182,33 +4422,36 @@
         <v>27</v>
       </c>
       <c r="G91" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H91" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I91" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J91">
         <v>10</v>
       </c>
       <c r="K91" t="s">
-        <v>34</v>
-      </c>
-      <c r="R91" t="s">
-        <v>31</v>
-      </c>
-      <c r="S91" t="s">
-        <v>70</v>
-      </c>
-      <c r="T91" t="s">
-        <v>85</v>
-      </c>
-      <c r="U91" t="s">
-        <v>35</v>
-      </c>
-      <c r="X91">
+        <v>38</v>
+      </c>
+      <c r="P91" t="s">
+        <v>68</v>
+      </c>
+      <c r="W91" t="s">
+        <v>35</v>
+      </c>
+      <c r="X91" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB91">
         <v>8</v>
       </c>
     </row>
@@ -4220,7 +4463,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -4232,24 +4475,27 @@
         <v>17</v>
       </c>
       <c r="G92" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I92" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J92">
         <v>5</v>
       </c>
       <c r="K92" t="s">
-        <v>34</v>
-      </c>
-      <c r="R92" t="s">
-        <v>31</v>
-      </c>
-      <c r="S92" t="s">
-        <v>59</v>
-      </c>
-      <c r="X92">
+        <v>38</v>
+      </c>
+      <c r="P92" t="s">
+        <v>68</v>
+      </c>
+      <c r="W92" t="s">
+        <v>35</v>
+      </c>
+      <c r="X92" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB92">
         <v>8</v>
       </c>
     </row>
@@ -4261,7 +4507,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -4273,33 +4519,36 @@
         <v>12</v>
       </c>
       <c r="G93" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H93" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I93" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J93">
         <v>0</v>
       </c>
       <c r="K93" t="s">
-        <v>40</v>
-      </c>
-      <c r="R93" t="s">
-        <v>31</v>
-      </c>
-      <c r="S93" t="s">
-        <v>70</v>
-      </c>
-      <c r="T93" t="s">
-        <v>71</v>
-      </c>
-      <c r="U93" t="s">
-        <v>31</v>
-      </c>
-      <c r="X93">
+        <v>45</v>
+      </c>
+      <c r="P93" t="s">
+        <v>68</v>
+      </c>
+      <c r="W93" t="s">
+        <v>35</v>
+      </c>
+      <c r="X93" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y93" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB93">
         <v>8</v>
       </c>
     </row>
@@ -4311,7 +4560,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D94">
         <v>2</v>
@@ -4323,36 +4572,39 @@
         <v>12</v>
       </c>
       <c r="G94" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H94" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I94" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="J94">
         <v>12</v>
       </c>
       <c r="K94" t="s">
-        <v>34</v>
-      </c>
-      <c r="R94" t="s">
-        <v>35</v>
-      </c>
-      <c r="S94" t="s">
-        <v>59</v>
-      </c>
-      <c r="T94" t="s">
-        <v>56</v>
-      </c>
-      <c r="U94" t="s">
-        <v>31</v>
-      </c>
-      <c r="V94" t="s">
-        <v>35</v>
-      </c>
-      <c r="X94">
+        <v>38</v>
+      </c>
+      <c r="P94" t="s">
+        <v>68</v>
+      </c>
+      <c r="W94" t="s">
+        <v>40</v>
+      </c>
+      <c r="X94" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y94" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA94" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB94">
         <v>8</v>
       </c>
     </row>
@@ -4364,7 +4616,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -4373,15 +4625,15 @@
         <v>3</v>
       </c>
       <c r="G95" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H95" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I95" t="s">
-        <v>62</v>
-      </c>
-      <c r="X95">
+        <v>72</v>
+      </c>
+      <c r="AB95">
         <v>8</v>
       </c>
     </row>
@@ -4393,19 +4645,19 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F96">
         <v>-40</v>
       </c>
       <c r="G96" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H96" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I96" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="97">
@@ -4416,7 +4668,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -4428,33 +4680,36 @@
         <v>-6</v>
       </c>
       <c r="G97" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H97" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I97" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J97">
         <v>3</v>
       </c>
       <c r="K97" t="s">
-        <v>34</v>
-      </c>
-      <c r="R97" t="s">
-        <v>48</v>
-      </c>
-      <c r="S97" t="s">
-        <v>49</v>
-      </c>
-      <c r="U97" t="s">
-        <v>31</v>
-      </c>
-      <c r="V97" t="s">
-        <v>31</v>
-      </c>
-      <c r="X97">
+        <v>38</v>
+      </c>
+      <c r="P97" t="s">
+        <v>54</v>
+      </c>
+      <c r="W97" t="s">
+        <v>55</v>
+      </c>
+      <c r="X97" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA97" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB97">
         <v>9</v>
       </c>
     </row>
@@ -4466,7 +4721,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D98">
         <v>2</v>
@@ -4478,30 +4733,33 @@
         <v>-9</v>
       </c>
       <c r="G98" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H98" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I98" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>34</v>
-      </c>
-      <c r="R98" t="s">
-        <v>35</v>
-      </c>
-      <c r="U98" t="s">
-        <v>35</v>
-      </c>
-      <c r="V98" t="s">
-        <v>35</v>
-      </c>
-      <c r="X98">
+        <v>38</v>
+      </c>
+      <c r="P98" t="s">
+        <v>54</v>
+      </c>
+      <c r="W98" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA98" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB98">
         <v>9</v>
       </c>
     </row>
@@ -4513,7 +4771,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D99">
         <v>3</v>
@@ -4525,33 +4783,36 @@
         <v>-9</v>
       </c>
       <c r="G99" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H99" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I99" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J99">
         <v>-2</v>
       </c>
       <c r="K99" t="s">
-        <v>34</v>
-      </c>
-      <c r="R99" t="s">
-        <v>35</v>
-      </c>
-      <c r="S99" t="s">
-        <v>65</v>
-      </c>
-      <c r="U99" t="s">
-        <v>31</v>
-      </c>
-      <c r="V99" t="s">
-        <v>31</v>
-      </c>
-      <c r="X99">
+        <v>38</v>
+      </c>
+      <c r="P99" t="s">
+        <v>54</v>
+      </c>
+      <c r="W99" t="s">
+        <v>40</v>
+      </c>
+      <c r="X99" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA99" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB99">
         <v>9</v>
       </c>
     </row>
@@ -4563,7 +4824,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D100">
         <v>4</v>
@@ -4575,15 +4836,15 @@
         <v>-7</v>
       </c>
       <c r="G100" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H100" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="I100" t="s">
-        <v>29</v>
-      </c>
-      <c r="X100">
+        <v>33</v>
+      </c>
+      <c r="AB100">
         <v>9</v>
       </c>
     </row>
@@ -4595,7 +4856,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -4607,18 +4868,18 @@
         <v>-46</v>
       </c>
       <c r="G101" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="I101" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J101">
         <v>0</v>
       </c>
       <c r="K101" t="s">
-        <v>40</v>
-      </c>
-      <c r="X101">
+        <v>45</v>
+      </c>
+      <c r="AB101">
         <v>9</v>
       </c>
     </row>
@@ -4630,7 +4891,7 @@
         <v>4</v>
       </c>
       <c r="C102" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -4642,33 +4903,36 @@
         <v>-46</v>
       </c>
       <c r="G102" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H102" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I102" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J102">
         <v>6</v>
       </c>
       <c r="K102" t="s">
-        <v>34</v>
-      </c>
-      <c r="R102" t="s">
-        <v>31</v>
-      </c>
-      <c r="S102" t="s">
-        <v>41</v>
-      </c>
-      <c r="T102" t="s">
-        <v>54</v>
-      </c>
-      <c r="U102" t="s">
-        <v>31</v>
-      </c>
-      <c r="X102">
+        <v>38</v>
+      </c>
+      <c r="P102" t="s">
+        <v>39</v>
+      </c>
+      <c r="W102" t="s">
+        <v>35</v>
+      </c>
+      <c r="X102" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y102" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB102">
         <v>9</v>
       </c>
     </row>
@@ -4680,7 +4944,7 @@
         <v>4</v>
       </c>
       <c r="C103" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -4692,33 +4956,36 @@
         <v>48</v>
       </c>
       <c r="G103" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H103" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I103" t="s">
+        <v>44</v>
+      </c>
+      <c r="J103">
+        <v>10</v>
+      </c>
+      <c r="K103" t="s">
+        <v>38</v>
+      </c>
+      <c r="P103" t="s">
         <v>39</v>
       </c>
-      <c r="J103">
-        <v>10</v>
-      </c>
-      <c r="K103" t="s">
-        <v>34</v>
-      </c>
-      <c r="R103" t="s">
-        <v>31</v>
-      </c>
-      <c r="S103" t="s">
-        <v>41</v>
-      </c>
-      <c r="T103" t="s">
-        <v>54</v>
-      </c>
-      <c r="U103" t="s">
-        <v>31</v>
-      </c>
-      <c r="X103">
+      <c r="W103" t="s">
+        <v>35</v>
+      </c>
+      <c r="X103" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y103" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB103">
         <v>9</v>
       </c>
     </row>
@@ -4730,7 +4997,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -4742,33 +5009,36 @@
         <v>38</v>
       </c>
       <c r="G104" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H104" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I104" t="s">
+        <v>44</v>
+      </c>
+      <c r="J104">
+        <v>3</v>
+      </c>
+      <c r="K104" t="s">
+        <v>45</v>
+      </c>
+      <c r="P104" t="s">
         <v>39</v>
       </c>
-      <c r="J104">
-        <v>3</v>
-      </c>
-      <c r="K104" t="s">
-        <v>40</v>
-      </c>
-      <c r="R104" t="s">
-        <v>31</v>
-      </c>
-      <c r="S104" t="s">
-        <v>41</v>
-      </c>
-      <c r="T104" t="s">
-        <v>43</v>
-      </c>
-      <c r="U104" t="s">
-        <v>31</v>
-      </c>
-      <c r="X104">
+      <c r="W104" t="s">
+        <v>35</v>
+      </c>
+      <c r="X104" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y104" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB104">
         <v>9</v>
       </c>
     </row>
@@ -4780,7 +5050,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -4792,33 +5062,36 @@
         <v>35</v>
       </c>
       <c r="G105" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H105" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I105" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J105">
         <v>11</v>
       </c>
       <c r="K105" t="s">
-        <v>34</v>
-      </c>
-      <c r="R105" t="s">
-        <v>35</v>
-      </c>
-      <c r="S105" t="s">
-        <v>41</v>
-      </c>
-      <c r="T105" t="s">
-        <v>42</v>
-      </c>
-      <c r="U105" t="s">
-        <v>35</v>
-      </c>
-      <c r="X105">
+        <v>38</v>
+      </c>
+      <c r="P105" t="s">
+        <v>39</v>
+      </c>
+      <c r="W105" t="s">
+        <v>40</v>
+      </c>
+      <c r="X105" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y105" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB105">
         <v>9</v>
       </c>
     </row>
@@ -4830,7 +5103,7 @@
         <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -4842,36 +5115,39 @@
         <v>24</v>
       </c>
       <c r="G106" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H106" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I106" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J106">
         <v>-1</v>
       </c>
       <c r="K106" t="s">
-        <v>40</v>
-      </c>
-      <c r="R106" t="s">
-        <v>35</v>
-      </c>
-      <c r="S106" t="s">
-        <v>41</v>
-      </c>
-      <c r="T106" t="s">
-        <v>86</v>
-      </c>
-      <c r="U106" t="s">
-        <v>35</v>
-      </c>
-      <c r="V106" t="s">
-        <v>31</v>
-      </c>
-      <c r="X106">
+        <v>45</v>
+      </c>
+      <c r="P106" t="s">
+        <v>97</v>
+      </c>
+      <c r="W106" t="s">
+        <v>40</v>
+      </c>
+      <c r="X106" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y106" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA106" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB106">
         <v>9</v>
       </c>
     </row>
@@ -4883,7 +5159,7 @@
         <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -4895,36 +5171,39 @@
         <v>25</v>
       </c>
       <c r="G107" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H107" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I107" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J107">
         <v>-9</v>
       </c>
       <c r="K107" t="s">
-        <v>40</v>
-      </c>
-      <c r="R107" t="s">
-        <v>35</v>
-      </c>
-      <c r="S107" t="s">
-        <v>87</v>
-      </c>
-      <c r="T107" t="s">
-        <v>88</v>
-      </c>
-      <c r="U107" t="s">
-        <v>31</v>
-      </c>
-      <c r="V107" t="s">
-        <v>31</v>
-      </c>
-      <c r="X107">
+        <v>45</v>
+      </c>
+      <c r="P107" t="s">
+        <v>68</v>
+      </c>
+      <c r="W107" t="s">
+        <v>40</v>
+      </c>
+      <c r="X107" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y107" t="s">
+        <v>100</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA107" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB107">
         <v>9</v>
       </c>
     </row>
@@ -4936,7 +5215,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D108">
         <v>2</v>
@@ -4948,33 +5227,36 @@
         <v>34</v>
       </c>
       <c r="G108" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H108" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I108" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J108">
         <v>0</v>
       </c>
       <c r="K108" t="s">
-        <v>40</v>
-      </c>
-      <c r="R108" t="s">
-        <v>35</v>
-      </c>
-      <c r="S108" t="s">
-        <v>75</v>
-      </c>
-      <c r="T108" t="s">
-        <v>42</v>
-      </c>
-      <c r="U108" t="s">
-        <v>31</v>
-      </c>
-      <c r="X108">
+        <v>45</v>
+      </c>
+      <c r="P108" t="s">
+        <v>68</v>
+      </c>
+      <c r="W108" t="s">
+        <v>40</v>
+      </c>
+      <c r="X108" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y108" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB108">
         <v>9</v>
       </c>
     </row>
@@ -4986,7 +5268,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D109">
         <v>3</v>
@@ -4998,33 +5280,36 @@
         <v>34</v>
       </c>
       <c r="G109" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H109" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I109" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="J109">
         <v>34</v>
       </c>
       <c r="K109" t="s">
-        <v>34</v>
-      </c>
-      <c r="R109" t="s">
-        <v>35</v>
-      </c>
-      <c r="S109" t="s">
-        <v>70</v>
-      </c>
-      <c r="T109" t="s">
-        <v>89</v>
-      </c>
-      <c r="U109" t="s">
-        <v>31</v>
-      </c>
-      <c r="X109">
+        <v>38</v>
+      </c>
+      <c r="P109" t="s">
+        <v>30</v>
+      </c>
+      <c r="W109" t="s">
+        <v>40</v>
+      </c>
+      <c r="X109" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y109" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB109">
         <v>9</v>
       </c>
     </row>
@@ -5036,21 +5321,21 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F110">
         <v>3</v>
       </c>
       <c r="G110" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H110" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I110" t="s">
-        <v>62</v>
-      </c>
-      <c r="X110">
+        <v>72</v>
+      </c>
+      <c r="AB110">
         <v>9</v>
       </c>
     </row>
@@ -5062,19 +5347,19 @@
         <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F111">
         <v>-40</v>
       </c>
       <c r="G111" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H111" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I111" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="112">
@@ -5085,7 +5370,7 @@
         <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -5097,33 +5382,36 @@
         <v>-32</v>
       </c>
       <c r="G112" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H112" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I112" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J112">
         <v>8</v>
       </c>
       <c r="K112" t="s">
-        <v>40</v>
-      </c>
-      <c r="R112" t="s">
-        <v>35</v>
-      </c>
-      <c r="S112" t="s">
-        <v>65</v>
-      </c>
-      <c r="U112" t="s">
-        <v>35</v>
-      </c>
-      <c r="V112" t="s">
-        <v>35</v>
-      </c>
-      <c r="X112">
+        <v>45</v>
+      </c>
+      <c r="P112" t="s">
+        <v>54</v>
+      </c>
+      <c r="W112" t="s">
+        <v>40</v>
+      </c>
+      <c r="X112" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z112" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA112" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB112">
         <v>10</v>
       </c>
     </row>
@@ -5135,7 +5423,7 @@
         <v>4</v>
       </c>
       <c r="C113" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D113">
         <v>2</v>
@@ -5147,33 +5435,36 @@
         <v>-40</v>
       </c>
       <c r="G113" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H113" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I113" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J113">
         <v>7</v>
       </c>
       <c r="K113" t="s">
-        <v>40</v>
-      </c>
-      <c r="R113" t="s">
-        <v>31</v>
-      </c>
-      <c r="S113" t="s">
-        <v>65</v>
-      </c>
-      <c r="U113" t="s">
-        <v>31</v>
-      </c>
-      <c r="V113" t="s">
-        <v>31</v>
-      </c>
-      <c r="X113">
+        <v>45</v>
+      </c>
+      <c r="P113" t="s">
+        <v>54</v>
+      </c>
+      <c r="W113" t="s">
+        <v>35</v>
+      </c>
+      <c r="X113" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA113" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB113">
         <v>10</v>
       </c>
     </row>
@@ -5185,7 +5476,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -5197,33 +5488,36 @@
         <v>-47</v>
       </c>
       <c r="G114" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H114" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I114" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>34</v>
-      </c>
-      <c r="R114" t="s">
-        <v>31</v>
-      </c>
-      <c r="S114" t="s">
-        <v>65</v>
-      </c>
-      <c r="U114" t="s">
-        <v>35</v>
-      </c>
-      <c r="V114" t="s">
-        <v>35</v>
-      </c>
-      <c r="X114">
+        <v>38</v>
+      </c>
+      <c r="P114" t="s">
+        <v>54</v>
+      </c>
+      <c r="W114" t="s">
+        <v>35</v>
+      </c>
+      <c r="X114" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA114" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB114">
         <v>10</v>
       </c>
     </row>
@@ -5235,7 +5529,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D115">
         <v>2</v>
@@ -5247,33 +5541,36 @@
         <v>-47</v>
       </c>
       <c r="G115" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H115" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I115" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J115">
         <v>3</v>
       </c>
       <c r="K115" t="s">
-        <v>34</v>
-      </c>
-      <c r="R115" t="s">
-        <v>48</v>
-      </c>
-      <c r="S115" t="s">
-        <v>90</v>
-      </c>
-      <c r="U115" t="s">
-        <v>35</v>
-      </c>
-      <c r="V115" t="s">
-        <v>35</v>
-      </c>
-      <c r="X115">
+        <v>38</v>
+      </c>
+      <c r="P115" t="s">
+        <v>54</v>
+      </c>
+      <c r="W115" t="s">
+        <v>55</v>
+      </c>
+      <c r="X115" t="s">
+        <v>102</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA115" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB115">
         <v>10</v>
       </c>
     </row>
@@ -5285,7 +5582,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D116">
         <v>3</v>
@@ -5297,33 +5594,36 @@
         <v>50</v>
       </c>
       <c r="G116" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H116" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I116" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="J116">
         <v>50</v>
       </c>
       <c r="K116" t="s">
-        <v>40</v>
-      </c>
-      <c r="R116" t="s">
-        <v>48</v>
-      </c>
-      <c r="S116" t="s">
-        <v>49</v>
-      </c>
-      <c r="U116" t="s">
-        <v>35</v>
-      </c>
-      <c r="V116" t="s">
-        <v>31</v>
-      </c>
-      <c r="X116">
+        <v>45</v>
+      </c>
+      <c r="P116" t="s">
+        <v>54</v>
+      </c>
+      <c r="W116" t="s">
+        <v>55</v>
+      </c>
+      <c r="X116" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z116" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA116" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB116">
         <v>10</v>
       </c>
     </row>
@@ -5335,21 +5635,21 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F117">
         <v>3</v>
       </c>
       <c r="G117" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H117" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="I117" t="s">
-        <v>62</v>
-      </c>
-      <c r="X117">
+        <v>72</v>
+      </c>
+      <c r="AB117">
         <v>10</v>
       </c>
     </row>
@@ -5361,19 +5661,19 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F118">
         <v>-40</v>
       </c>
       <c r="G118" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H118" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="I118" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="119">
@@ -5384,7 +5684,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -5396,33 +5696,36 @@
         <v>-34</v>
       </c>
       <c r="G119" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H119" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I119" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J119">
         <v>19</v>
       </c>
       <c r="K119" t="s">
-        <v>40</v>
-      </c>
-      <c r="R119" t="s">
-        <v>48</v>
-      </c>
-      <c r="S119" t="s">
-        <v>49</v>
-      </c>
-      <c r="U119" t="s">
-        <v>35</v>
-      </c>
-      <c r="V119" t="s">
-        <v>35</v>
-      </c>
-      <c r="X119">
+        <v>45</v>
+      </c>
+      <c r="P119" t="s">
+        <v>54</v>
+      </c>
+      <c r="W119" t="s">
+        <v>55</v>
+      </c>
+      <c r="X119" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA119" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB119">
         <v>11</v>
       </c>
     </row>
@@ -5434,7 +5737,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -5446,33 +5749,36 @@
         <v>47</v>
       </c>
       <c r="G120" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H120" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I120" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J120">
         <v>8</v>
       </c>
       <c r="K120" t="s">
-        <v>40</v>
-      </c>
-      <c r="R120" t="s">
-        <v>48</v>
-      </c>
-      <c r="S120" t="s">
-        <v>49</v>
-      </c>
-      <c r="U120" t="s">
-        <v>31</v>
-      </c>
-      <c r="V120" t="s">
-        <v>35</v>
-      </c>
-      <c r="X120">
+        <v>45</v>
+      </c>
+      <c r="P120" t="s">
+        <v>54</v>
+      </c>
+      <c r="W120" t="s">
+        <v>55</v>
+      </c>
+      <c r="X120" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z120" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA120" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB120">
         <v>11</v>
       </c>
     </row>
@@ -5484,7 +5790,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D121">
         <v>2</v>
@@ -5496,33 +5802,36 @@
         <v>39</v>
       </c>
       <c r="G121" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H121" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I121" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J121">
         <v>5</v>
       </c>
       <c r="K121" t="s">
-        <v>40</v>
-      </c>
-      <c r="R121" t="s">
-        <v>48</v>
-      </c>
-      <c r="S121" t="s">
-        <v>49</v>
-      </c>
-      <c r="U121" t="s">
-        <v>31</v>
-      </c>
-      <c r="V121" t="s">
-        <v>31</v>
-      </c>
-      <c r="X121">
+        <v>45</v>
+      </c>
+      <c r="P121" t="s">
+        <v>54</v>
+      </c>
+      <c r="W121" t="s">
+        <v>55</v>
+      </c>
+      <c r="X121" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA121" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB121">
         <v>11</v>
       </c>
     </row>
@@ -5534,7 +5843,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -5546,33 +5855,36 @@
         <v>34</v>
       </c>
       <c r="G122" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H122" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I122" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J122">
         <v>5</v>
       </c>
       <c r="K122" t="s">
-        <v>40</v>
-      </c>
-      <c r="R122" t="s">
-        <v>48</v>
-      </c>
-      <c r="S122" t="s">
-        <v>49</v>
-      </c>
-      <c r="U122" t="s">
-        <v>31</v>
-      </c>
-      <c r="V122" t="s">
-        <v>31</v>
-      </c>
-      <c r="X122">
+        <v>45</v>
+      </c>
+      <c r="P122" t="s">
+        <v>54</v>
+      </c>
+      <c r="W122" t="s">
+        <v>55</v>
+      </c>
+      <c r="X122" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>35</v>
+      </c>
+      <c r="AA122" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB122">
         <v>11</v>
       </c>
     </row>
@@ -5584,7 +5896,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D123">
         <v>2</v>
@@ -5596,33 +5908,36 @@
         <v>29</v>
       </c>
       <c r="G123" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H123" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I123" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J123">
         <v>-5</v>
       </c>
       <c r="K123" t="s">
-        <v>34</v>
-      </c>
-      <c r="R123" t="s">
-        <v>48</v>
-      </c>
-      <c r="S123" t="s">
-        <v>49</v>
-      </c>
-      <c r="U123" t="s">
-        <v>35</v>
-      </c>
-      <c r="V123" t="s">
-        <v>35</v>
-      </c>
-      <c r="X123">
+        <v>38</v>
+      </c>
+      <c r="P123" t="s">
+        <v>54</v>
+      </c>
+      <c r="W123" t="s">
+        <v>55</v>
+      </c>
+      <c r="X123" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA123" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB123">
         <v>11</v>
       </c>
     </row>
@@ -5634,10 +5949,10 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>25</v>
-      </c>
-      <c r="R124" t="s">
-        <v>48</v>
+        <v>29</v>
+      </c>
+      <c r="W124" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="125">
@@ -5648,7 +5963,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D125">
         <v>3</v>
@@ -5660,33 +5975,36 @@
         <v>34</v>
       </c>
       <c r="G125" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H125" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I125" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J125">
         <v>10</v>
       </c>
       <c r="K125" t="s">
-        <v>40</v>
-      </c>
-      <c r="R125" t="s">
-        <v>48</v>
-      </c>
-      <c r="S125" t="s">
-        <v>49</v>
-      </c>
-      <c r="U125" t="s">
-        <v>35</v>
-      </c>
-      <c r="V125" t="s">
-        <v>31</v>
-      </c>
-      <c r="X125">
+        <v>45</v>
+      </c>
+      <c r="P125" t="s">
+        <v>54</v>
+      </c>
+      <c r="W125" t="s">
+        <v>55</v>
+      </c>
+      <c r="X125" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z125" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA125" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB125">
         <v>11</v>
       </c>
     </row>
@@ -5698,7 +6016,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -5710,33 +6028,36 @@
         <v>24</v>
       </c>
       <c r="G126" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H126" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I126" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="J126">
         <v>0</v>
       </c>
       <c r="K126" t="s">
-        <v>34</v>
-      </c>
-      <c r="R126" t="s">
-        <v>31</v>
-      </c>
-      <c r="S126" t="s">
-        <v>65</v>
-      </c>
-      <c r="U126" t="s">
-        <v>35</v>
-      </c>
-      <c r="V126" t="s">
-        <v>35</v>
-      </c>
-      <c r="X126">
+        <v>38</v>
+      </c>
+      <c r="P126" t="s">
+        <v>54</v>
+      </c>
+      <c r="W126" t="s">
+        <v>35</v>
+      </c>
+      <c r="X126" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA126" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB126">
         <v>11</v>
       </c>
     </row>
